--- a/Data Files/EDEN/CheckPoints List.xlsx
+++ b/Data Files/EDEN/CheckPoints List.xlsx
@@ -25,7 +25,7 @@
     <t>Chithra</t>
   </si>
   <si>
-    <t>Privilege Leave</t>
+    <t>Privilege/Annual Leave</t>
   </si>
   <si>
     <t>Majunath</t>
